--- a/human_adjudication/human_adjudication_v_2_4_1/reviewer_runs/2025/R_A/human_adjudication_v_2_4_1_2025_R_A_completed.xlsx
+++ b/human_adjudication/human_adjudication_v_2_4_1/reviewer_runs/2025/R_A/human_adjudication_v_2_4_1_2025_R_A_completed.xlsx
@@ -26,6 +26,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C_jama.2024.24764'!$A$1:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'C_jama.2024.27643'!$A$1:$R$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'C_jama.2025.11178'!$A$1:$R$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'C_jama.2025.15185'!$A$1:$R$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'C_jama.2025.15440'!$A$1:$R$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'C_jama.2025.16450'!$A$1:$R$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'C_jama.2025.19563'!$A$1:$R$14</definedName>
@@ -129,7 +131,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -226,7 +228,6 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -9437,7 +9438,7 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" ht="55" customFormat="1" customHeight="1" s="14">
@@ -9447,7 +9448,7 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('C_jama.2024.24764'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2024.27643'!$G$2:$G$17,"PRIMARY READY")+COUNTIF('C_jama.2025.15440'!$G$2:$G$2,"PRIMARY READY")+COUNTIF('C_jama.2025.16450'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.19563'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.19843'!$G$2:$G$8,"PRIMARY READY")+COUNTIF('C_jama.2025.20765'!$G$2:$G$20,"PRIMARY READY")+COUNTIF('C_jama.2025.24175'!$G$2:$G$15,"PRIMARY READY")+COUNTIF('C_jama.2025.4390'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.7583'!$G$2:$G$5,"PRIMARY READY")+COUNTIF('C_jama.2025.7710'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9110'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9663'!$G$2:$G$6,"PRIMARY READY")</f>
+        <f>COUNTIF('C_jama.2024.24764'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2024.27643'!$G$2:$G$17,"PRIMARY READY")+COUNTIF('C_jama.2025.11178'!$G$2:$G$19,"PRIMARY READY")+COUNTIF('C_jama.2025.15185'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.15440'!$G$2:$G$2,"PRIMARY READY")+COUNTIF('C_jama.2025.16450'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.19563'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.19843'!$G$2:$G$8,"PRIMARY READY")+COUNTIF('C_jama.2025.20765'!$G$2:$G$20,"PRIMARY READY")+COUNTIF('C_jama.2025.24175'!$G$2:$G$15,"PRIMARY READY")+COUNTIF('C_jama.2025.4390'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.7583'!$G$2:$G$5,"PRIMARY READY")+COUNTIF('C_jama.2025.7710'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9110'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9663'!$G$2:$G$6,"PRIMARY READY")</f>
         <v/>
       </c>
     </row>
@@ -9458,7 +9459,7 @@
         </is>
       </c>
       <c r="B5" s="17">
-        <f>COUNTIF('C_jama.2024.24764'!$D$2:$D$6,"discuss")+COUNTIF('C_jama.2024.27643'!$D$2:$D$17,"discuss")+COUNTIF('C_jama.2025.15440'!$D$2:$D$2,"discuss")+COUNTIF('C_jama.2025.16450'!$D$2:$D$7,"discuss")+COUNTIF('C_jama.2025.19563'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.19843'!$D$2:$D$8,"discuss")+COUNTIF('C_jama.2025.20765'!$D$2:$D$20,"discuss")+COUNTIF('C_jama.2025.24175'!$D$2:$D$15,"discuss")+COUNTIF('C_jama.2025.4390'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.7583'!$D$2:$D$5,"discuss")+COUNTIF('C_jama.2025.7710'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9110'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9663'!$D$2:$D$6,"discuss")</f>
+        <f>COUNTIF('C_jama.2024.24764'!$D$2:$D$6,"discuss")+COUNTIF('C_jama.2024.27643'!$D$2:$D$17,"discuss")+COUNTIF('C_jama.2025.11178'!$D$2:$D$19,"discuss")+COUNTIF('C_jama.2025.15185'!$D$2:$D$7,"discuss")+COUNTIF('C_jama.2025.15440'!$D$2:$D$2,"discuss")+COUNTIF('C_jama.2025.16450'!$D$2:$D$7,"discuss")+COUNTIF('C_jama.2025.19563'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.19843'!$D$2:$D$8,"discuss")+COUNTIF('C_jama.2025.20765'!$D$2:$D$20,"discuss")+COUNTIF('C_jama.2025.24175'!$D$2:$D$15,"discuss")+COUNTIF('C_jama.2025.4390'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.7583'!$D$2:$D$5,"discuss")+COUNTIF('C_jama.2025.7710'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9110'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9663'!$D$2:$D$6,"discuss")</f>
         <v/>
       </c>
     </row>
@@ -9519,13 +9520,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="14" min="1" max="1"/>
     <col width="38" customWidth="1" style="14" min="2" max="2"/>
     <col width="18" customWidth="1" style="14" min="3" max="3"/>
-    <col width="60" customWidth="1" style="25" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customFormat="1" customHeight="1" s="14">
@@ -9544,11 +9544,6 @@
           <t>Candidates</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="36" customHeight="1" s="25">
       <c r="A2" s="16" t="inlineStr">
@@ -9592,12 +9587,7 @@
         </is>
       </c>
       <c r="C4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Placeholder: workflow 1.6.2 output pending; no candidates in this version</t>
-        </is>
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" s="25">
@@ -9612,12 +9602,7 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Placeholder: workflow 1.6.2 output pending; no candidates in this version</t>
-        </is>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" s="25">
@@ -11542,7 +11527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="14" min="1" max="1"/>
@@ -11637,15 +11622,1295 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>Placeholder: no workflow 1.6.2 output for this paper yet; nothing to review in v.2.4.1.</t>
+    <row r="2" ht="92" customHeight="1" s="25">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C001</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Planned versus reported online session duration</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Yes, all five locations: REPORT main p.3, Health Coach Program and Online Program — jama_debar_2025_oi_250046_1755300121.13587.pdf; PLAN protocol p.43 §10.1.1 — joi250046supp1_prod_1755300121.14087.pdf and p.44 coach overview — joi250046supp1_prod_1755300121.14087.pdf; REPORT TIDieR p.3 Procedures — joi250046supp3_prod_1755300121.15087.pdf and p.4 When and How Much — joi250046supp3_prod_1755300121.15087.pdf.</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G2" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$19,A2)&lt;&gt;1,LEFT(A2,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J2" s="22">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L2" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M2" s="20" t="n"/>
+      <c r="N2" s="23" t="n"/>
+      <c r="O2" s="23" t="n"/>
+      <c r="P2" s="23" t="n"/>
+      <c r="Q2" s="23" t="n"/>
+      <c r="R2" s="22" t="inlineStr">
+        <is>
+          <t>Protocol v5.0 p43 (10.1.1): painTRAINER sessions take 45-60 min; p44 (10.1.2): coach sessions take 60 min. Main p3 and TIDieR supp3 pp3-4: painTRAINER 30-45 min, coach 45-60 min. Session number (8) and 12-week window unchanged. Described per-session dose is shorter in the report for both arms (non-overlapping for painTRAINER); may reflect a revised completion-time estimate rather than changed content. Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="92" customHeight="1" s="25">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C002</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Therapeutic-dose adherence percentage</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.4 Results adherence paragraph — jama_debar_2025_oi_250046_1755300121.13587.pdf and p.5 Figure 1 PT allocation/session counts — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G3" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$19,A3)&lt;&gt;1,LEFT(A3,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J3" s="22" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="K3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),OR(E3="report_internal_inconsistency",E3="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L3" s="22">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M3" s="24" t="n"/>
+      <c r="N3" s="23" t="n"/>
+      <c r="O3" s="23" t="n"/>
+      <c r="P3" s="23" t="n"/>
+      <c r="Q3" s="23" t="n"/>
+      <c r="R3" s="22" t="inlineStr">
+        <is>
+          <t>Main p4: painTRAINER '371 (43%) completed at least 6 sessions'. Figure 1 p5: 776 randomized; 371 + 156 + 249 = 776. 371/776 = 47.8% (printed 43%); 371/527 initiators = 70.4%. Other three adherence percentages reproduce (527/776 = 67.9%, 660/778 = 84.8%, 548/778 = 70.4%). Count is correct, percentage wrong. Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1" s="25">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C003</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>SMD construction across Table 3</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.4 SMD definition — jama_debar_2025_oi_250046_1755300121.13587.pdf, p.10 Table 3 — jama_debar_2025_oi_250046_1755300121.13587.pdf, and p.11 continuation and footnote d — jama_debar_2025_oi_250046_1755300121.13587.pdf. All twenty registered outcome/time rows and all three point-contrast columns per row were read directly.</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G4" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$19,A4)&lt;&gt;1,LEFT(A4,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>substantive</t>
+        </is>
+      </c>
+      <c r="J4" s="22" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),OR(E4="report_internal_inconsistency",E4="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L4" s="22">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M4" s="20" t="n"/>
+      <c r="N4" s="23" t="n"/>
+      <c r="O4" s="23" t="n"/>
+      <c r="P4" s="23" t="n"/>
+      <c r="Q4" s="23" t="n"/>
+      <c r="R4" s="22" t="inlineStr">
+        <is>
+          <t>Main p4 and Table 3 note d (p11): SMD = adjusted MD / SD of UC change at that time point, so the three contrasts at a time point share one denominator. Recomputed for all 21 rows: implied SD (MD/SMD) differs across the three columns of one row (e.g., social 3 mo: 6.7, 150, 3.5), 4 SMDs have the opposite sign to their MD, HC-PT SMD is -0.08 to -0.13 where MD is 0.0, and SMD(HC-PT) is not SMD(HC-UC) - SMD(PT-UC) in 17 rows. SMD columns cannot follow the stated definition. Also: text p7 quotes 3-month SMDs -0.26/-0.36, which are the 6-month values in Table 3 (3-month: -0.25/-0.34). Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1" s="25">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C004</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Reciprocal NNT point-reproduction pattern</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.4 NNT definition — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT main p.9 Table 2 severity 6-month HC/UC, interference 6-month HC/UC and footnote d — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT results p.14 eTable 8 reminder-letter 6-month PT/UC and footnote d — joi250046supp4_prod_1755300121.15587.pdf. All three affected rows were read.</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>exclude</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$19,A5)&lt;&gt;1,LEFT(A5,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),OR(E5="report_internal_inconsistency",E5="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="23" t="n"/>
+      <c r="O5" s="23" t="n"/>
+      <c r="P5" s="23" t="n"/>
+      <c r="Q5" s="23" t="n"/>
+      <c r="R5" s="22" t="inlineStr">
+        <is>
+          <t>Main p4 and Table 2 note d: NNT = 1/(difference in adjusted %). Recomputed all 81 NNT points in Table 2 and eTables 7-8 with +/-0.05 on each displayed %: every printed NNT equals the round-up (ceiling) of 1/RD, and 24 of 81 (including the 3 flagged) are incompatible with conventional rounding. Rounding NNT up is the standard convention and is applied consistently. Card names upward rounding as an alternative; my full-table check settles it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1" s="25">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C005</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Age as a prespecified base adjustment covariate</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Yes: PLAN protocol p.56 §15.5 — joi250046supp1_prod_1755300121.14087.pdf; PLAN SAP p.20 §§13–14 — joi250046supp2_prod_1755300121.15087.pdf; REPORT main p.4 adjustment sentence — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT results p.4 Adjustment — joi250046supp4_prod_1755300121.15587.pdf, p.7 eTable 2 all-model variables — joi250046supp4_prod_1755300121.15587.pdf, p.8 eTable 3 age — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 age — joi250046supp4_prod_1755300121.15587.pdf, p.10 eTable 5 age — joi250046supp4_prod_1755300121.15587.pdf; REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet eTable 3, cells G2, A10, G10, directly decoded.</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G6" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$19,A6)&lt;&gt;1,LEFT(A6,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J6" s="22">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),OR(E6="report_internal_inconsistency",E6="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="23" t="n"/>
+      <c r="O6" s="23" t="n"/>
+      <c r="P6" s="23" t="n"/>
+      <c r="Q6" s="23" t="n"/>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>Protocol v5.0 PDF p56 (section 15.5) and SAP v6.0 p20 (14.0): adjust for baseline pain severity, sex, site, rural residence, multisite pain, mental health condition (no age). Main p4 gives the same list. Supp4 p4 and eTable 2 p7 call age part of the 'base set of pre-specified adjustment variables'; eTables 3-4 fit age &gt;=65; xlsx eTable 3 G10 marks age as prespecified. Age was added to all primary models and described as prespecified. Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1" s="25">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C006</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Secondary-analysis adjustment specification</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>Yes: PLAN protocol p.57 §15.6 — joi250046supp1_prod_1755300121.14087.pdf; PLAN SAP p.21 §15 — joi250046supp2_prod_1755300121.15087.pdf; REPORT main p.4 secondary methods — jama_debar_2025_oi_250046_1755300121.13587.pdf, p.10 Table 3 — jama_debar_2025_oi_250046_1755300121.13587.pdf and p.11 continuation — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$19,A7)&lt;&gt;1,LEFT(A7,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J7" s="22">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),OR(E7="report_internal_inconsistency",E7="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L7" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+      <c r="R7" s="22" t="inlineStr">
+        <is>
+          <t>Protocol PDF p57 (section 15.6) and SAP p21 (section 15.0): secondary analyses 'follow the same approach as Aim 1' and 'include as covariates baseline levels of pain severity and all stratification variables'. Main p4: same structures 'with added adjustment for the given baseline secondary outcome'. The baseline value of each secondary outcome is an added covariate not in either plan. Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1" s="25">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C007</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Primary versus sensitivity missing-data analysis roles</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Yes: PLAN SAP p.19 §11 — joi250046supp2_prod_1755300121.15087.pdf, PLAN p.4 July 17, 2024 amendment — joi250046supp2_prod_1755300121.15087.pdf; REPORT main p.4 missing-data paragraph — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT results p.4 Missing Data — joi250046supp4_prod_1755300121.15587.pdf, p.5 Non-Response Weighting — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 — joi250046supp4_prod_1755300121.15587.pdf, p.11 sensitivity narrative and complete-case block — joi250046supp4_prod_1755300121.15587.pdf. P.5 was read as disclosed-amendment context in addition to the registered comparisons.</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G8" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A8="",COUNTIF($A$2:$A$19,A8)&lt;&gt;1,LEFT(A8,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D8="retain",E8="statistical_results")),H8&lt;&gt;"",NOT(EXACT(H8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),I8&lt;&gt;"",NOT(EXACT(I8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),J8&lt;&gt;"",NOT(EXACT(J8,"not_applicable"))),AND(NOT(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material"))),K8&lt;&gt;"",NOT(EXACT(K8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="protocol_report")),L8&lt;&gt;"",NOT(EXACT(L8,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D8,"retain"),EXACT(D8,"exclude"),EXACT(D8,"discuss"))),NOT(OR(EXACT(E8,"statistical_results"),EXACT(E8,"report_internal_inconsistency"),EXACT(E8,"plan_material"),EXACT(E8,"protocol_report"))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(H8,"confirmed_issue"),EXACT(H8,"probable_issue"),EXACT(H8,"not_issue"),EXACT(H8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(I8,"substantive"),EXACT(I8,"minor_presentation"),EXACT(I8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),J8&lt;&gt;"",NOT(OR(EXACT(J8,"direct"),EXACT(J8,"possible"),EXACT(J8,"unlikely"),EXACT(J8,"unknown")))),AND(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material")),NOT(OR(EXACT(K8,"substantive_inconsistency"),EXACT(K8,"minor_presentation"),EXACT(K8,"non_inconsistency"),EXACT(K8,"indeterminate")))),AND(AND(D8="retain",E8="protocol_report"),L8&lt;&gt;"",NOT(OR(EXACT(L8,"substantive_difference"),EXACT(L8,"minor_presentation"),EXACT(L8,"version_timing"),EXACT(L8,"non_inconsistency"),EXACT(L8,"indeterminate"))))),"CHECK FIELDS",IF(AND(F8&lt;&gt;"",NOT(OR(EXACT(F8,"no"),EXACT(F8,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F8,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J8" s="22">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),OR(E8="report_internal_inconsistency",E8="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>indeterminate</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="23" t="n"/>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="23" t="n"/>
+      <c r="Q8" s="23" t="n"/>
+      <c r="R8" s="22" t="inlineStr">
+        <is>
+          <t>SAP v6.0 (18 Jul 2024) p19 section 11: 'For the primary analyses, we will analyze those patients who have follow-up data' under MAR; if &gt;15% missing or differential, pattern-mixture imputation plus IPW (IPW added by the 17 Jul 2024 amendment, p4, after follow-up ended Apr 2024) and worst/best-case sensitivity. Report (main p4; supp4 pp4-5, 11): weighted MNAR imputation is primary; complete-case labelled a 'pre-specified sensitivity analysis'. Disclosed (supp4 p5). The conditional clause can be read as authorizing the switch, so the plan's own hierarchy is ambiguous.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="92" customHeight="1" s="25">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C008</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>RR versus finite NNT null coverage</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.9 Table 2 HC/PT columns and footnotes b,d,e — jama_debar_2025_oi_250046_1755300121.13587.pdf, all six registered contrast/time rows; REPORT p.4 binary model and NNT method — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G9" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A9="",COUNTIF($A$2:$A$19,A9)&lt;&gt;1,LEFT(A9,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D9="retain",E9="statistical_results")),H9&lt;&gt;"",NOT(EXACT(H9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),I9&lt;&gt;"",NOT(EXACT(I9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),J9&lt;&gt;"",NOT(EXACT(J9,"not_applicable"))),AND(NOT(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material"))),K9&lt;&gt;"",NOT(EXACT(K9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="protocol_report")),L9&lt;&gt;"",NOT(EXACT(L9,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D9,"retain"),EXACT(D9,"exclude"),EXACT(D9,"discuss"))),NOT(OR(EXACT(E9,"statistical_results"),EXACT(E9,"report_internal_inconsistency"),EXACT(E9,"plan_material"),EXACT(E9,"protocol_report"))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(H9,"confirmed_issue"),EXACT(H9,"probable_issue"),EXACT(H9,"not_issue"),EXACT(H9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(I9,"substantive"),EXACT(I9,"minor_presentation"),EXACT(I9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),J9&lt;&gt;"",NOT(OR(EXACT(J9,"direct"),EXACT(J9,"possible"),EXACT(J9,"unlikely"),EXACT(J9,"unknown")))),AND(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material")),NOT(OR(EXACT(K9,"substantive_inconsistency"),EXACT(K9,"minor_presentation"),EXACT(K9,"non_inconsistency"),EXACT(K9,"indeterminate")))),AND(AND(D9="retain",E9="protocol_report"),L9&lt;&gt;"",NOT(OR(EXACT(L9,"substantive_difference"),EXACT(L9,"minor_presentation"),EXACT(L9,"version_timing"),EXACT(L9,"non_inconsistency"),EXACT(L9,"indeterminate"))))),"CHECK FIELDS",IF(AND(F9&lt;&gt;"",NOT(OR(EXACT(F9,"no"),EXACT(F9,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F9,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>substantive</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="K9" s="21">
+        <f>IF(AND(OR(D9="retain",D9=""),OR(E9="report_internal_inconsistency",E9="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L9" s="22">
+        <f>IF(AND(OR(D9="retain",D9=""),E9="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="23" t="n"/>
+      <c r="O9" s="23" t="n"/>
+      <c r="P9" s="23" t="n"/>
+      <c r="Q9" s="23" t="n"/>
+      <c r="R9" s="22" t="inlineStr">
+        <is>
+          <t>Main p9 Table 2: the six HC-vs-PT rows whose RR CI includes 1 (severity 6/12 mo, intensity 3/12 mo, interference 6/12 mo) print finite positive NNT CIs (e.g., 24 (12-186)), implying RD CIs above 0. In the text layer exactly these six use an en dash (U+2013) and all 21 others a hyphen. Reading the en dash as a lost minus (12 to -186) gives RD lower limits of -0.54, -1.32, -1.75, -2.63, -1.49, -1.27 points, matching those implied by the RR CIs (-0.66, -1.44, -1.70, -2.57, -1.48, -1.19) and footnote e. Printed intervals misstate null coverage. Beyond the card, which did not identify the mechanism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="92" customHeight="1" s="25">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C009</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>NNT point outside its confidence interval</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.9 Table 2 pain intensity 12 months, HC/PT NNT column — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G10" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A10="",COUNTIF($A$2:$A$19,A10)&lt;&gt;1,LEFT(A10,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D10="retain",E10="statistical_results")),H10&lt;&gt;"",NOT(EXACT(H10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),I10&lt;&gt;"",NOT(EXACT(I10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),J10&lt;&gt;"",NOT(EXACT(J10,"not_applicable"))),AND(NOT(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material"))),K10&lt;&gt;"",NOT(EXACT(K10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="protocol_report")),L10&lt;&gt;"",NOT(EXACT(L10,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D10,"retain"),EXACT(D10,"exclude"),EXACT(D10,"discuss"))),NOT(OR(EXACT(E10,"statistical_results"),EXACT(E10,"report_internal_inconsistency"),EXACT(E10,"plan_material"),EXACT(E10,"protocol_report"))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(H10,"confirmed_issue"),EXACT(H10,"probable_issue"),EXACT(H10,"not_issue"),EXACT(H10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(I10,"substantive"),EXACT(I10,"minor_presentation"),EXACT(I10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),J10&lt;&gt;"",NOT(OR(EXACT(J10,"direct"),EXACT(J10,"possible"),EXACT(J10,"unlikely"),EXACT(J10,"unknown")))),AND(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material")),NOT(OR(EXACT(K10,"substantive_inconsistency"),EXACT(K10,"minor_presentation"),EXACT(K10,"non_inconsistency"),EXACT(K10,"indeterminate")))),AND(AND(D10="retain",E10="protocol_report"),L10&lt;&gt;"",NOT(OR(EXACT(L10,"substantive_difference"),EXACT(L10,"minor_presentation"),EXACT(L10,"version_timing"),EXACT(L10,"non_inconsistency"),EXACT(L10,"indeterminate"))))),"CHECK FIELDS",IF(AND(F10&lt;&gt;"",NOT(OR(EXACT(F10,"no"),EXACT(F10,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F10,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>substantive</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="K10" s="21">
+        <f>IF(AND(OR(D10="retain",D10=""),OR(E10="report_internal_inconsistency",E10="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L10" s="22">
+        <f>IF(AND(OR(D10="retain",D10=""),E10="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="23" t="n"/>
+      <c r="O10" s="23" t="n"/>
+      <c r="P10" s="23" t="n"/>
+      <c r="Q10" s="23" t="n"/>
+      <c r="R10" s="22" t="inlineStr">
+        <is>
+          <t>Main p9 Table 2, pain intensity 12 mo HC vs PT: NNT 63 (18-38), point outside interval. 1/(33.7 - 32.1) = 62.5, so 63 is correct; RR 1.05 (0.92-1.20) includes 1. Same lost-minus mechanism as C008 (en dash): intended interval 18 to -38, i.e., RD -2.6 to 5.6 points. As printed the interval is impossible and also implies a significant RD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="92" customHeight="1" s="25">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C010</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>SMD points outside printed confidence intervals</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.10 Table 3 — jama_debar_2025_oi_250046_1755300121.13587.pdf and p.11 PGIC-pain continuation — jama_debar_2025_oi_250046_1755300121.13587.pdf. Every one of the fourteen registered tuples was read directly; all matched the ledger.</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G11" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A11="",COUNTIF($A$2:$A$19,A11)&lt;&gt;1,LEFT(A11,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D11="retain",E11="statistical_results")),H11&lt;&gt;"",NOT(EXACT(H11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),I11&lt;&gt;"",NOT(EXACT(I11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),J11&lt;&gt;"",NOT(EXACT(J11,"not_applicable"))),AND(NOT(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material"))),K11&lt;&gt;"",NOT(EXACT(K11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="protocol_report")),L11&lt;&gt;"",NOT(EXACT(L11,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D11,"retain"),EXACT(D11,"exclude"),EXACT(D11,"discuss"))),NOT(OR(EXACT(E11,"statistical_results"),EXACT(E11,"report_internal_inconsistency"),EXACT(E11,"plan_material"),EXACT(E11,"protocol_report"))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(H11,"confirmed_issue"),EXACT(H11,"probable_issue"),EXACT(H11,"not_issue"),EXACT(H11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(I11,"substantive"),EXACT(I11,"minor_presentation"),EXACT(I11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),J11&lt;&gt;"",NOT(OR(EXACT(J11,"direct"),EXACT(J11,"possible"),EXACT(J11,"unlikely"),EXACT(J11,"unknown")))),AND(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material")),NOT(OR(EXACT(K11,"substantive_inconsistency"),EXACT(K11,"minor_presentation"),EXACT(K11,"non_inconsistency"),EXACT(K11,"indeterminate")))),AND(AND(D11="retain",E11="protocol_report"),L11&lt;&gt;"",NOT(OR(EXACT(L11,"substantive_difference"),EXACT(L11,"minor_presentation"),EXACT(L11,"version_timing"),EXACT(L11,"non_inconsistency"),EXACT(L11,"indeterminate"))))),"CHECK FIELDS",IF(AND(F11&lt;&gt;"",NOT(OR(EXACT(F11,"no"),EXACT(F11,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F11,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>substantive</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="K11" s="21">
+        <f>IF(AND(OR(D11="retain",D11=""),OR(E11="report_internal_inconsistency",E11="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L11" s="22">
+        <f>IF(AND(OR(D11="retain",D11=""),E11="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="23" t="n"/>
+      <c r="Q11" s="23" t="n"/>
+      <c r="R11" s="22" t="inlineStr">
+        <is>
+          <t>Main pp10-11 Table 3: I count 14 of 63 SMD points outside their printed 95% CIs (severity 12 mo PT/UC -0.25 (-0.24 to 0.01); physical 6 and 12 mo all three; PGIC pain 12 mo all three; etc.) and 18 intervals with reversed limits (all social and physical rows). Same root problem as C003 (SMD columns do not follow the stated construction). Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="92" customHeight="1" s="25">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C011</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Covariate set of restricted primary analyses</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.4 Adjustment — joi250046supp4_prod_1755300121.15587.pdf, p.7 eTable 2 final imputation/estimation set — joi250046supp4_prod_1755300121.15587.pdf, p.13 Protocol Change Subset Analyses — joi250046supp4_prod_1755300121.15587.pdf, p.14 eTable 8 all three blocks and footnote b — joi250046supp4_prod_1755300121.15587.pdf. Fitted education/employment terms at p.8 — joi250046supp4_prod_1755300121.15587.pdf and p.9 — joi250046supp4_prod_1755300121.15587.pdf were also read as corroboration.</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G12" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A12="",COUNTIF($A$2:$A$19,A12)&lt;&gt;1,LEFT(A12,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D12="retain",E12="statistical_results")),H12&lt;&gt;"",NOT(EXACT(H12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),I12&lt;&gt;"",NOT(EXACT(I12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),J12&lt;&gt;"",NOT(EXACT(J12,"not_applicable"))),AND(NOT(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material"))),K12&lt;&gt;"",NOT(EXACT(K12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="protocol_report")),L12&lt;&gt;"",NOT(EXACT(L12,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D12,"retain"),EXACT(D12,"exclude"),EXACT(D12,"discuss"))),NOT(OR(EXACT(E12,"statistical_results"),EXACT(E12,"report_internal_inconsistency"),EXACT(E12,"plan_material"),EXACT(E12,"protocol_report"))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(H12,"confirmed_issue"),EXACT(H12,"probable_issue"),EXACT(H12,"not_issue"),EXACT(H12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(I12,"substantive"),EXACT(I12,"minor_presentation"),EXACT(I12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),J12&lt;&gt;"",NOT(OR(EXACT(J12,"direct"),EXACT(J12,"possible"),EXACT(J12,"unlikely"),EXACT(J12,"unknown")))),AND(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material")),NOT(OR(EXACT(K12,"substantive_inconsistency"),EXACT(K12,"minor_presentation"),EXACT(K12,"non_inconsistency"),EXACT(K12,"indeterminate")))),AND(AND(D12="retain",E12="protocol_report"),L12&lt;&gt;"",NOT(OR(EXACT(L12,"substantive_difference"),EXACT(L12,"minor_presentation"),EXACT(L12,"version_timing"),EXACT(L12,"non_inconsistency"),EXACT(L12,"indeterminate"))))),"CHECK FIELDS",IF(AND(F12&lt;&gt;"",NOT(OR(EXACT(F12,"no"),EXACT(F12,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F12,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>probable_issue</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J12" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K12" s="21">
+        <f>IF(AND(OR(D12="retain",D12=""),OR(E12="report_internal_inconsistency",E12="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L12" s="22">
+        <f>IF(AND(OR(D12="retain",D12=""),E12="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="23" t="n"/>
+      <c r="O12" s="23" t="n"/>
+      <c r="P12" s="23" t="n"/>
+      <c r="Q12" s="23" t="n"/>
+      <c r="R12" s="22" t="inlineStr">
+        <is>
+          <t>Supp4 p13 calls eTable 8 'the primary analysis restricting to subsets'; eTable 2 p7 and eTables 3-4 add education and employment to the primary imputation/estimation models. eTable 8 note b (p14) lists only sex, age, site, rural, multisite, mental health, baseline pain severity (copied from eTable 7, the complete-case analysis). Either the footnote is incomplete or the subset models are not the primary model. Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="92" customHeight="1" s="25">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C012</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Final response-weight model predictor membership</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.4 Adjustment/selection — joi250046supp4_prod_1755300121.15587.pdf, p.5 Non-Response Weighting — joi250046supp4_prod_1755300121.15587.pdf, p.7 eTable 2 final nonresponse predictors — joi250046supp4_prod_1755300121.15587.pdf, p.10 eTable 5 full coefficient display — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet eTable 3, cells A18, H18, I18, J18.</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G13" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A13="",COUNTIF($A$2:$A$19,A13)&lt;&gt;1,LEFT(A13,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D13="retain",E13="statistical_results")),H13&lt;&gt;"",NOT(EXACT(H13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),I13&lt;&gt;"",NOT(EXACT(I13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),J13&lt;&gt;"",NOT(EXACT(J13,"not_applicable"))),AND(NOT(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material"))),K13&lt;&gt;"",NOT(EXACT(K13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="protocol_report")),L13&lt;&gt;"",NOT(EXACT(L13,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D13,"retain"),EXACT(D13,"exclude"),EXACT(D13,"discuss"))),NOT(OR(EXACT(E13,"statistical_results"),EXACT(E13,"report_internal_inconsistency"),EXACT(E13,"plan_material"),EXACT(E13,"protocol_report"))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(H13,"confirmed_issue"),EXACT(H13,"probable_issue"),EXACT(H13,"not_issue"),EXACT(H13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(I13,"substantive"),EXACT(I13,"minor_presentation"),EXACT(I13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),J13&lt;&gt;"",NOT(OR(EXACT(J13,"direct"),EXACT(J13,"possible"),EXACT(J13,"unlikely"),EXACT(J13,"unknown")))),AND(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material")),NOT(OR(EXACT(K13,"substantive_inconsistency"),EXACT(K13,"minor_presentation"),EXACT(K13,"non_inconsistency"),EXACT(K13,"indeterminate")))),AND(AND(D13="retain",E13="protocol_report"),L13&lt;&gt;"",NOT(OR(EXACT(L13,"substantive_difference"),EXACT(L13,"minor_presentation"),EXACT(L13,"version_timing"),EXACT(L13,"non_inconsistency"),EXACT(L13,"indeterminate"))))),"CHECK FIELDS",IF(AND(F13&lt;&gt;"",NOT(OR(EXACT(F13,"no"),EXACT(F13,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F13,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K13" s="21">
+        <f>IF(AND(OR(D13="retain",D13=""),OR(E13="report_internal_inconsistency",E13="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L13" s="22">
+        <f>IF(AND(OR(D13="retain",D13=""),E13="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M13" s="24" t="n"/>
+      <c r="N13" s="23" t="n"/>
+      <c r="O13" s="23" t="n"/>
+      <c r="P13" s="23" t="n"/>
+      <c r="Q13" s="23" t="n"/>
+      <c r="R13" s="22" t="inlineStr">
+        <is>
+          <t>Supp4 eTable 2 p7: additional weight-model predictors PEG, PHQ-8, GAD-7, any negative SDOH, education. Fitted weight model eTable 5 p10: PEG, PHQ-8, GAD-7, no negative SDOH, not employed; no education. xlsx eTable 3: education has no non-response P (I12 blank; H12 .0156, J12 .05), employment qualifies (H18 &lt;.001, I18 .0228). eTable 5 matches the stated selection rule; eTable 2 names the wrong variable. Card agrees on the conflict; xlsx resolves which is right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="92" customHeight="1" s="25">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C013</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Education coding and coefficient attribution</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.7 eTable 2 final primary predictor list — joi250046supp4_prod_1755300121.15587.pdf, p.8 eTable 3 all three education rows — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 all three education rows — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet eTable 3, cells A12:A16.</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G14" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A14="",COUNTIF($A$2:$A$19,A14)&lt;&gt;1,LEFT(A14,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D14="retain",E14="statistical_results")),H14&lt;&gt;"",NOT(EXACT(H14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),I14&lt;&gt;"",NOT(EXACT(I14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),J14&lt;&gt;"",NOT(EXACT(J14,"not_applicable"))),AND(NOT(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material"))),K14&lt;&gt;"",NOT(EXACT(K14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="protocol_report")),L14&lt;&gt;"",NOT(EXACT(L14,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D14,"retain"),EXACT(D14,"exclude"),EXACT(D14,"discuss"))),NOT(OR(EXACT(E14,"statistical_results"),EXACT(E14,"report_internal_inconsistency"),EXACT(E14,"plan_material"),EXACT(E14,"protocol_report"))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(H14,"confirmed_issue"),EXACT(H14,"probable_issue"),EXACT(H14,"not_issue"),EXACT(H14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(I14,"substantive"),EXACT(I14,"minor_presentation"),EXACT(I14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),J14&lt;&gt;"",NOT(OR(EXACT(J14,"direct"),EXACT(J14,"possible"),EXACT(J14,"unlikely"),EXACT(J14,"unknown")))),AND(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material")),NOT(OR(EXACT(K14,"substantive_inconsistency"),EXACT(K14,"minor_presentation"),EXACT(K14,"non_inconsistency"),EXACT(K14,"indeterminate")))),AND(AND(D14="retain",E14="protocol_report"),L14&lt;&gt;"",NOT(OR(EXACT(L14,"substantive_difference"),EXACT(L14,"minor_presentation"),EXACT(L14,"version_timing"),EXACT(L14,"non_inconsistency"),EXACT(L14,"indeterminate"))))),"CHECK FIELDS",IF(AND(F14&lt;&gt;"",NOT(OR(EXACT(F14,"no"),EXACT(F14,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F14,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K14" s="21">
+        <f>IF(AND(OR(D14="retain",D14=""),OR(E14="report_internal_inconsistency",E14="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L14" s="22">
+        <f>IF(AND(OR(D14="retain",D14=""),E14="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M14" s="20" t="n"/>
+      <c r="N14" s="23" t="n"/>
+      <c r="O14" s="23" t="n"/>
+      <c r="P14" s="23" t="n"/>
+      <c r="Q14" s="23" t="n"/>
+      <c r="R14" s="22" t="inlineStr">
+        <is>
+          <t>Supp4 eTable 2 p7: education selected as binary (any college vs HS or less). eTables 3-4 (pp8-9) show three education coefficients vs HS or less, two labelled 'AA degree' (e.g., eTable 4 RR 0.97 and 1.16). xlsx eTable 3 has four levels (HS or less, Associate's/Technical, College, Doctoral/Postgraduate), consistent with a 4-level term; the second 'AA' row is presumably College degree. Coding description and labels conflict. Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="92" customHeight="1" s="25">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C014</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Coefficient CI versus P-value null-significance pattern</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.8 eTable 3 seven registered rows — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 age and second AA rows — joi250046supp4_prod_1755300121.15587.pdf, p.10 eTable 5 PEG row — joi250046supp4_prod_1755300121.15587.pdf. Method context was read at results p.4 — joi250046supp4_prod_1755300121.15587.pdf, p.5 — joi250046supp4_prod_1755300121.15587.pdf, and REPORT main p.4 two-sided alpha=.05 — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G15" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A15="",COUNTIF($A$2:$A$19,A15)&lt;&gt;1,LEFT(A15,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D15="retain",E15="statistical_results")),H15&lt;&gt;"",NOT(EXACT(H15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="statistical_results")),I15&lt;&gt;"",NOT(EXACT(I15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="statistical_results")),J15&lt;&gt;"",NOT(EXACT(J15,"not_applicable"))),AND(NOT(AND(D15="retain",OR(E15="report_internal_inconsistency",E15="plan_material"))),K15&lt;&gt;"",NOT(EXACT(K15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="protocol_report")),L15&lt;&gt;"",NOT(EXACT(L15,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D15,"retain"),EXACT(D15,"exclude"),EXACT(D15,"discuss"))),NOT(OR(EXACT(E15,"statistical_results"),EXACT(E15,"report_internal_inconsistency"),EXACT(E15,"plan_material"),EXACT(E15,"protocol_report"))),AND(AND(D15="retain",E15="statistical_results"),NOT(OR(EXACT(H15,"confirmed_issue"),EXACT(H15,"probable_issue"),EXACT(H15,"not_issue"),EXACT(H15,"indeterminate")))),AND(AND(D15="retain",E15="statistical_results"),NOT(OR(EXACT(I15,"substantive"),EXACT(I15,"minor_presentation"),EXACT(I15,"indeterminate")))),AND(AND(D15="retain",E15="statistical_results"),J15&lt;&gt;"",NOT(OR(EXACT(J15,"direct"),EXACT(J15,"possible"),EXACT(J15,"unlikely"),EXACT(J15,"unknown")))),AND(AND(D15="retain",OR(E15="report_internal_inconsistency",E15="plan_material")),NOT(OR(EXACT(K15,"substantive_inconsistency"),EXACT(K15,"minor_presentation"),EXACT(K15,"non_inconsistency"),EXACT(K15,"indeterminate")))),AND(AND(D15="retain",E15="protocol_report"),L15&lt;&gt;"",NOT(OR(EXACT(L15,"substantive_difference"),EXACT(L15,"minor_presentation"),EXACT(L15,"version_timing"),EXACT(L15,"non_inconsistency"),EXACT(L15,"indeterminate"))))),"CHECK FIELDS",IF(AND(F15&lt;&gt;"",NOT(OR(EXACT(F15,"no"),EXACT(F15,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F15,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J15" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K15" s="21">
+        <f>IF(AND(OR(D15="retain",D15=""),OR(E15="report_internal_inconsistency",E15="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L15" s="22">
+        <f>IF(AND(OR(D15="retain",D15=""),E15="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M15" s="24" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+      <c r="R15" s="22" t="inlineStr">
+        <is>
+          <t>Supp4 eTable 3 p8: across all 20 rows with exact P, the z implied by the CI is about 1.94 times the z implied by P (median ratio 1.94); printed P values match what each 'CI' would give if it were est +/- 1 SE (e.g., Pattern 2: 0.151 vs printed .150; Site 3: .070 vs .069). So the eTable 3 intervals are not 95% Wald intervals for the printed P values (likely +/-1 SE intervals, or P from a 1.96-fold SE). The three flagged ratio rows (eTable 4 age and second AA, eTable 5 PEG) reproduce within display rounding. Goes beyond the card on mechanism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="92" customHeight="1" s="25">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C015</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Within-header three-month subset counts</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.14 eTable 8 first subgroup header — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT p.7 eTable 1 — joi250046supp4_prod_1755300121.15587.pdf, p.13 subset definition — joi250046supp4_prod_1755300121.15587.pdf, and the second/third headers on p.14.</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G16" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A16="",COUNTIF($A$2:$A$19,A16)&lt;&gt;1,LEFT(A16,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D16="retain",E16="statistical_results")),H16&lt;&gt;"",NOT(EXACT(H16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="statistical_results")),I16&lt;&gt;"",NOT(EXACT(I16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="statistical_results")),J16&lt;&gt;"",NOT(EXACT(J16,"not_applicable"))),AND(NOT(AND(D16="retain",OR(E16="report_internal_inconsistency",E16="plan_material"))),K16&lt;&gt;"",NOT(EXACT(K16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="protocol_report")),L16&lt;&gt;"",NOT(EXACT(L16,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D16,"retain"),EXACT(D16,"exclude"),EXACT(D16,"discuss"))),NOT(OR(EXACT(E16,"statistical_results"),EXACT(E16,"report_internal_inconsistency"),EXACT(E16,"plan_material"),EXACT(E16,"protocol_report"))),AND(AND(D16="retain",E16="statistical_results"),NOT(OR(EXACT(H16,"confirmed_issue"),EXACT(H16,"probable_issue"),EXACT(H16,"not_issue"),EXACT(H16,"indeterminate")))),AND(AND(D16="retain",E16="statistical_results"),NOT(OR(EXACT(I16,"substantive"),EXACT(I16,"minor_presentation"),EXACT(I16,"indeterminate")))),AND(AND(D16="retain",E16="statistical_results"),J16&lt;&gt;"",NOT(OR(EXACT(J16,"direct"),EXACT(J16,"possible"),EXACT(J16,"unlikely"),EXACT(J16,"unknown")))),AND(AND(D16="retain",OR(E16="report_internal_inconsistency",E16="plan_material")),NOT(OR(EXACT(K16,"substantive_inconsistency"),EXACT(K16,"minor_presentation"),EXACT(K16,"non_inconsistency"),EXACT(K16,"indeterminate")))),AND(AND(D16="retain",E16="protocol_report"),L16&lt;&gt;"",NOT(OR(EXACT(L16,"substantive_difference"),EXACT(L16,"minor_presentation"),EXACT(L16,"version_timing"),EXACT(L16,"non_inconsistency"),EXACT(L16,"indeterminate"))))),"CHECK FIELDS",IF(AND(F16&lt;&gt;"",NOT(OR(EXACT(F16,"no"),EXACT(F16,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F16,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J16" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K16" s="21">
+        <f>IF(AND(OR(D16="retain",D16=""),OR(E16="report_internal_inconsistency",E16="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L16" s="22">
+        <f>IF(AND(OR(D16="retain",D16=""),E16="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="23" t="n"/>
+      <c r="O16" s="23" t="n"/>
+      <c r="P16" s="23" t="n"/>
+      <c r="Q16" s="23" t="n"/>
+      <c r="R16" s="22" t="inlineStr">
+        <is>
+          <t>Supp4 eTable 8 p14 first header: 'N=454; 366 with at least 1 follow-up; PT=149, HC=153, UC=152 at 3-months'. 149 + 153 + 152 = 454 = N randomized, exceeding 366. These are arm sizes, not 3-month counts; eTable 1 minus the post-enhancement block gives 3-month counts UC 109, PT 94, HC 108 (311). Other two headers are coherent (1487 &lt;= 1670; 858 &lt;= 935). Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="92" customHeight="1" s="25">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C016</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Raw-score summary statistic and bounds in eTable 11</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.15 Additional Unadjusted Data and Analyses — joi250046supp4_prod_1755300121.15587.pdf, p.17 eTable 11 title/header and all 21 rows — joi250046supp4_prod_1755300121.15587.pdf, p.18 note b — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT main p.11 PGIC footnotes h/i — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G17" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A17="",COUNTIF($A$2:$A$19,A17)&lt;&gt;1,LEFT(A17,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D17="retain",E17="statistical_results")),H17&lt;&gt;"",NOT(EXACT(H17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),I17&lt;&gt;"",NOT(EXACT(I17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),J17&lt;&gt;"",NOT(EXACT(J17,"not_applicable"))),AND(NOT(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material"))),K17&lt;&gt;"",NOT(EXACT(K17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="protocol_report")),L17&lt;&gt;"",NOT(EXACT(L17,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D17,"retain"),EXACT(D17,"exclude"),EXACT(D17,"discuss"))),NOT(OR(EXACT(E17,"statistical_results"),EXACT(E17,"report_internal_inconsistency"),EXACT(E17,"plan_material"),EXACT(E17,"protocol_report"))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(H17,"confirmed_issue"),EXACT(H17,"probable_issue"),EXACT(H17,"not_issue"),EXACT(H17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(I17,"substantive"),EXACT(I17,"minor_presentation"),EXACT(I17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),J17&lt;&gt;"",NOT(OR(EXACT(J17,"direct"),EXACT(J17,"possible"),EXACT(J17,"unlikely"),EXACT(J17,"unknown")))),AND(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material")),NOT(OR(EXACT(K17,"substantive_inconsistency"),EXACT(K17,"minor_presentation"),EXACT(K17,"non_inconsistency"),EXACT(K17,"indeterminate")))),AND(AND(D17="retain",E17="protocol_report"),L17&lt;&gt;"",NOT(OR(EXACT(L17,"substantive_difference"),EXACT(L17,"minor_presentation"),EXACT(L17,"version_timing"),EXACT(L17,"non_inconsistency"),EXACT(L17,"indeterminate"))))),"CHECK FIELDS",IF(AND(F17&lt;&gt;"",NOT(OR(EXACT(F17,"no"),EXACT(F17,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F17,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>substantive</t>
+        </is>
+      </c>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="K17" s="21">
+        <f>IF(AND(OR(D17="retain",D17=""),OR(E17="report_internal_inconsistency",E17="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L17" s="22">
+        <f>IF(AND(OR(D17="retain",D17=""),E17="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="23" t="n"/>
+      <c r="O17" s="23" t="n"/>
+      <c r="P17" s="23" t="n"/>
+      <c r="Q17" s="23" t="n"/>
+      <c r="R17" s="22" t="inlineStr">
+        <is>
+          <t>Supp4 p15 calls eTable 11 'unadjusted mean' outcomes; p17 title/header say median (25th, 75th percentile). Most cells (e.g., social role 43.4 (42.8, 44.0)) are far too narrow to be IQRs of T-scores (SD about 7) and behave like means with 95% CIs; two PGIC cells (2.0 (1.0, 3.0); 2.0 (1.0, 2.0)) look like medians/IQRs. Beyond the card: in all 21 rows the three raw columns reproduce the printed MDs only if ordered UC, PT, HC (max deviation &lt;= 0.1), not as labelled PT, HC, UC (deviations 0.6-3.3). Arm labels and statistic type are both wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="92" customHeight="1" s="25">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C017</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Workbook All Observed depression percentage</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Yes: supplied REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet exactly eTable 3, E3, A82, E82, A83, E83, A110. Direct workbook.xml confirms worksheet name and worksheet relationship; direct sheet1.xml/sharedStrings.xml confirms all cells. B82/C82/D82 were also read as count-partition corroboration.</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G18" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A18="",COUNTIF($A$2:$A$19,A18)&lt;&gt;1,LEFT(A18,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D18="retain",E18="statistical_results")),H18&lt;&gt;"",NOT(EXACT(H18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),I18&lt;&gt;"",NOT(EXACT(I18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),J18&lt;&gt;"",NOT(EXACT(J18,"not_applicable"))),AND(NOT(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material"))),K18&lt;&gt;"",NOT(EXACT(K18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="protocol_report")),L18&lt;&gt;"",NOT(EXACT(L18,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D18,"retain"),EXACT(D18,"exclude"),EXACT(D18,"discuss"))),NOT(OR(EXACT(E18,"statistical_results"),EXACT(E18,"report_internal_inconsistency"),EXACT(E18,"plan_material"),EXACT(E18,"protocol_report"))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(H18,"confirmed_issue"),EXACT(H18,"probable_issue"),EXACT(H18,"not_issue"),EXACT(H18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(I18,"substantive"),EXACT(I18,"minor_presentation"),EXACT(I18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),J18&lt;&gt;"",NOT(OR(EXACT(J18,"direct"),EXACT(J18,"possible"),EXACT(J18,"unlikely"),EXACT(J18,"unknown")))),AND(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material")),NOT(OR(EXACT(K18,"substantive_inconsistency"),EXACT(K18,"minor_presentation"),EXACT(K18,"non_inconsistency"),EXACT(K18,"indeterminate")))),AND(AND(D18="retain",E18="protocol_report"),L18&lt;&gt;"",NOT(OR(EXACT(L18,"substantive_difference"),EXACT(L18,"minor_presentation"),EXACT(L18,"version_timing"),EXACT(L18,"non_inconsistency"),EXACT(L18,"indeterminate"))))),"CHECK FIELDS",IF(AND(F18&lt;&gt;"",NOT(OR(EXACT(F18,"no"),EXACT(F18,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F18,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K18" s="21">
+        <f>IF(AND(OR(D18="retain",D18=""),OR(E18="report_internal_inconsistency",E18="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L18" s="22">
+        <f>IF(AND(OR(D18="retain",D18=""),E18="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M18" s="20" t="n"/>
+      <c r="N18" s="23" t="n"/>
+      <c r="O18" s="23" t="n"/>
+      <c r="P18" s="23" t="n"/>
+      <c r="Q18" s="23" t="n"/>
+      <c r="R18" s="22" t="inlineStr">
+        <is>
+          <t>Supp5 xlsx sheet eTable 3, E82: 'Current depression (PHQ-8 &gt;=10)' All Observed 711 (73.2); E3 N=1568, E83 missing 2; footnote A110: missing excluded from denominator. 711/1566 = 45.4%. Counts partition correctly (162 + 243 + 711 = 1116 = B82). Percentage wrong; count correct. Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="92" customHeight="1" s="25">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C018</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Physical-function omnibus P values and contrast intervals</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>Results supplement PDF p17, eTable 11 Physical Functioning 6 months — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Results supplement PDF p17, eTable 11 Physical Functioning 12 months — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Results supplement PDF p17, all other 19 eTable 11 outcome/time rows — joi250046supp4_prod_1755300121.15587.pdf (REPORT, same-display corroboration); Results supplement PDF p18, eTable 11 note b — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Results supplement PDF page 15, Additional Unadjusted Data and Analyses — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Main article PDF p11, Table 3 note c — jama_debar_2025_oi_250046_1755300121.13587.pdf (REPORT, corroboration only); Main article PDF p4, Statistical Analysis — jama_debar_2025_oi_250046_1755300121.13587.pdf (REPORT, corroboration only); The rendered p17 heading is unadjusted between-group mean differences (95%CI), with PT vs UC, HC vs UC and HC vs PT columns and a separately named omnibus P column. No pairwise P value is printed. The comparison does not equate raw medians with fitted means, and does not equate a single pairwise null with the omnibus null</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G19" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A19="",COUNTIF($A$2:$A$19,A19)&lt;&gt;1,LEFT(A19,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D19="retain",E19="statistical_results")),H19&lt;&gt;"",NOT(EXACT(H19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),I19&lt;&gt;"",NOT(EXACT(I19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),J19&lt;&gt;"",NOT(EXACT(J19,"not_applicable"))),AND(NOT(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material"))),K19&lt;&gt;"",NOT(EXACT(K19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="protocol_report")),L19&lt;&gt;"",NOT(EXACT(L19,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D19,"retain"),EXACT(D19,"exclude"),EXACT(D19,"discuss"))),NOT(OR(EXACT(E19,"statistical_results"),EXACT(E19,"report_internal_inconsistency"),EXACT(E19,"plan_material"),EXACT(E19,"protocol_report"))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(H19,"confirmed_issue"),EXACT(H19,"probable_issue"),EXACT(H19,"not_issue"),EXACT(H19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(I19,"substantive"),EXACT(I19,"minor_presentation"),EXACT(I19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),J19&lt;&gt;"",NOT(OR(EXACT(J19,"direct"),EXACT(J19,"possible"),EXACT(J19,"unlikely"),EXACT(J19,"unknown")))),AND(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material")),NOT(OR(EXACT(K19,"substantive_inconsistency"),EXACT(K19,"minor_presentation"),EXACT(K19,"non_inconsistency"),EXACT(K19,"indeterminate")))),AND(AND(D19="retain",E19="protocol_report"),L19&lt;&gt;"",NOT(OR(EXACT(L19,"substantive_difference"),EXACT(L19,"minor_presentation"),EXACT(L19,"version_timing"),EXACT(L19,"non_inconsistency"),EXACT(L19,"indeterminate"))))),"CHECK FIELDS",IF(AND(F19&lt;&gt;"",NOT(OR(EXACT(F19,"no"),EXACT(F19,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F19,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>probable_issue</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J19" s="22" t="inlineStr">
+        <is>
+          <t>unlikely</t>
+        </is>
+      </c>
+      <c r="K19" s="21">
+        <f>IF(AND(OR(D19="retain",D19=""),OR(E19="report_internal_inconsistency",E19="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L19" s="22">
+        <f>IF(AND(OR(D19="retain",D19=""),E19="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="23" t="n"/>
+      <c r="O19" s="23" t="n"/>
+      <c r="P19" s="23" t="n"/>
+      <c r="Q19" s="23" t="n"/>
+      <c r="R19" s="22" t="inlineStr">
+        <is>
+          <t>Supp4 eTable 11 p17, physical function: the covariance of the two UC contrasts is identified from the three contrast CIs (Cov = (v1 + v2 - v3)/2), so the 2-df Wald omnibus can be rebuilt without an independence assumption. Reconstructed P = .025 (6 mo; printed .005) and .010 (12 mo; printed .001); over the full rounding box the minimum is about .009 and .003, still above the printed values. 3-month (.18 vs .212) and social role rows reproduce. Both printed and rebuilt P are &lt; .05, so the LSD gate is unchanged. Probable: assumes the omnibus used the same robust covariance as the contrasts. Card agrees.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R19"/>
+  <conditionalFormatting sqref="H2:H19">
+    <cfRule type="expression" priority="8" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I19">
+    <cfRule type="expression" priority="9" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J19">
+    <cfRule type="expression" priority="10" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K19">
+    <cfRule type="expression" priority="11" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),OR($E2="report_internal_inconsistency",$E2="plan_material")))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L19">
+    <cfRule type="expression" priority="12" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="protocol_report"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G19">
+    <cfRule type="expression" priority="13" dxfId="71">
+      <formula>G2&lt;&gt;"PRIMARY READY"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation sqref="D2:D19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"retain,exclude,discuss"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"statistical_results,report_internal_inconsistency,plan_material,protocol_report"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"no,primary_done"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"confirmed_issue,probable_issue,not_issue,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive,minor_presentation,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"direct,possible,unlikely,unknown,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_inconsistency,minor_presentation,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_difference,minor_presentation,version_timing,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11656,7 +12921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="14" min="1" max="1"/>
@@ -11751,15 +13016,470 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>Placeholder: no workflow 1.6.2 output for this paper yet; nothing to review in v.2.4.1.</t>
+    <row r="2" ht="92" customHeight="1" s="25">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C001</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>PROMIS-29 scalar scoring and direction are not specified</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 3, Secondary Outcomes: domain definition and direction; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Secondary Outcomes: single scalar result; joi250066supp3_prod_1761597796.4701.pdf — p. 15, eTable 4, PROMIS 29 row: corroborating scalar and adjusted result; joi250066supp1_prod_1761597796.4601.pdf — p. 70, PROMIS assessment: contextual scale description</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G2" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$7,A2)&lt;&gt;1,LEFT(A2,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H2" s="21" t="inlineStr">
+        <is>
+          <t>confirmed_issue</t>
+        </is>
+      </c>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>substantive</t>
+        </is>
+      </c>
+      <c r="J2" s="22" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="K2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L2" s="22">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M2" s="20" t="n"/>
+      <c r="N2" s="23" t="n"/>
+      <c r="O2" s="23" t="n"/>
+      <c r="P2" s="23" t="n"/>
+      <c r="Q2" s="23" t="n"/>
+      <c r="R2" s="22" t="inlineStr">
+        <is>
+          <t>Main p3: PROMIS-29 has 7 domains (raw 4-20 each), higher scores better in some and worse in others. Main p6 and eTable 4 (supp3 p15) report one PROMIS-29 score (levodopa 66 (14) text, 64.74 (14.33) eTable 4; placebo 65 (14) / 65.11 (13.79)) and MD -0.37 (-3.34 to 2.61). No scoring rule, range or direction for this single score in the article, protocol (p70 v1.4 / OCR) or SAP. A sum of mixed-direction raw domains is not interpretable, and the sign of the MD cannot be read. Text 66 also does not round from 64.74. Card agrees; the text-table mismatch is additional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="92" customHeight="1" s="25">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C002</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Primary analysis population changes from all randomized participants to survivors</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>joi250066supp1_prod_1761597796.4601.pdf — p. 86, §§11.4.1–11.4.2: FAS and primary assignment; joi250066supp1_prod_1761597796.4601.pdf — p. 87, §11.5: missing-data rule; joi250066supp2_prod_1761597796.4701.pdf — p. 4, §3.2 and footnote: deceased participants' contribution; joi250066supp2_prod_1761597796.4701.pdf — p. 6, §4.3: primary/supportive status; joi250066supp2_prod_1761597796.4701.pdf — p. 7, §§4.3.1–4.3.3: primary versus death-inclusive strategy; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 4, Statistical Analyses: survivor-primary rule; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, flow and SAP explanation: participant totals and timing; joi250066supp3_prod_1761597796.4701.pdf — p. 12, population definitions: primary death exclusion; joi250066supp3_prod_1761597796.4701.pdf — p. 13, eTable 2, estimands 1, 3 and 4: primary and death-inclusive results</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G3" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$7,A3)&lt;&gt;1,LEFT(A3,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J3" s="22">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),OR(E3="report_internal_inconsistency",E3="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L3" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M3" s="24" t="n"/>
+      <c r="N3" s="23" t="n"/>
+      <c r="O3" s="23" t="n"/>
+      <c r="P3" s="23" t="n"/>
+      <c r="Q3" s="23" t="n"/>
+      <c r="R3" s="22" t="inlineStr">
+        <is>
+          <t>Protocol v1.4 (28 Feb 2023) p86 11.4.1: FAS = all randomized, ITT; 11.5: missing data by MI. SAP (signed 27 Sep 2024, after last visit 27 Aug 2024, before database closure 15 Oct 2024) p4 3.2 and footnote: deaths before visit 3 are in the FAS but contribute only to estimand 3 and the composite. Report p4: primary analysis excludes the 28 deaths (11 vs 17); n = 582. Death-inclusive estimands (3, 4, 10) are supportive. Partly disclosed (main p5: SAP differs from protocol in 'statistical terminology'). Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1" s="25">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C003</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Primary mixed-model terms are absent from the implemented linear model</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>joi250066supp1_prod_1761597796.4601.pdf — p. 56, statistical synopsis: final mixed-model summary; joi250066supp1_prod_1761597796.4601.pdf — p. 86, §11.4.2: final primary formula/variance structure; joi250066supp2_prod_1761597796.4701.pdf — p. 10, §5.2: baseline/treatment linear model; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 4, Statistical Analyses: reported model; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, alignment explanation: SAP timing and alignment context; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Primary Outcome: affected primary result; joi250066supp5_prod_1761597796.4751.pdf — p. 1, code lines 19–26 and 31–32: explicit implementation and pooling; joi250066supp1_prod_1761597796.4601.pdf — p. 10, earlier synopsis: historical center-term context; joi250066supp1_prod_1761597796.4601.pdf — p. 39, earlier §11.4.2: historical center-term context</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G4" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$7,A4)&lt;&gt;1,LEFT(A4,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J4" s="22">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),OR(E4="report_internal_inconsistency",E4="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L4" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M4" s="20" t="n"/>
+      <c r="N4" s="23" t="n"/>
+      <c r="O4" s="23" t="n"/>
+      <c r="P4" s="23" t="n"/>
+      <c r="Q4" s="23" t="n"/>
+      <c r="R4" s="22" t="inlineStr">
+        <is>
+          <t>Protocol v1.4 p56 (synopsis) and p86 11.4.2: mixed model with baseline FMA, treatment and stroke type as fixed effects and a random intercept for center (v1.1 pp10, 39: same without stroke type). SAP p10 5.2, main p4 and code (supp5 lines 22-23: lm(FMA3 ~ baseline + medication), pooled by mice) fit baseline + treatment only. Center (a randomization stratum) and stroke type dropped. Not specifically disclosed. Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1" s="25">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C004</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Secondary missing-data procedures differ from the SAP rule</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>joi250066supp2_prod_1761597796.4701.pdf — p. 5, §4.2: secondary-outcome status; joi250066supp2_prod_1761597796.4701.pdf — p. 11, §6: general imputation rule; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, secondary methods: reported nonimputation; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, mRS/PRAI results: affected outcomes; joi250066supp3_prod_1761597796.4701.pdf — p. 7, deviations: mRS death assignment and PRAI exception; joi250066supp3_prod_1761597796.4701.pdf — p. 15, eTable 4: mRS/PRAI results and populations</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$7,A5)&lt;&gt;1,LEFT(A5,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),OR(E5="report_internal_inconsistency",E5="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L5" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="23" t="n"/>
+      <c r="O5" s="23" t="n"/>
+      <c r="P5" s="23" t="n"/>
+      <c r="Q5" s="23" t="n"/>
+      <c r="R5" s="22" t="inlineStr">
+        <is>
+          <t>SAP p11 section 6: missing secondary outcomes imputed as for the primary (100 MICE imputations); only harm outcomes not imputed. Main p5: mRS and PRAI missing data not imputed; supp3 p7 lists these as SAP deviations (deaths set to mRS 6; PRAI not imputed). eTable 4: mRS n = 596, PRAI n = 546 vs 582 for other secondaries. Disclosed (supp3 p7). Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1" s="25">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C005</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Planned primary-endpoint supplementary analyses are not identified in the report</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>joi250066supp1_prod_1761597796.4601.pdf — p. 86, §§11.4.1 and 11.4.3: primary sensitivities and bounded PP context; joi250066supp2_prod_1761597796.4701.pdf — p. 11, §7: center interaction model; joi250066supp2_prod_1761597796.4701.pdf — p. 12, §7.2: seven-variable subgroup package; joi250066supp2_prod_1761597796.4701.pdf — p. 15, addendum: subgroup directions and median splits; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 4, supplementary/post hoc estimands: reported analysis and adherence context; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, subgroup/center/spline methods: related reported analyses and prespecification statement; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, primary/sensitivity results: affected primary analysis package; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 7, Additional Post Hoc Analyses: baseline analyses; joi250066supp3_prod_1761597796.4701.pdf — p. 1, complete display index: nine eTables and seven eFigures; joi250066supp3_prod_1761597796.4701.pdf — p. 13, eTable 2: eight prespecified estimands; joi250066supp3_prod_1761597796.4701.pdf — p. 14, eTable 3: post hoc estimands; joi250066supp3_prod_1761597796.4701.pdf — p. 18, eTables 7–8: baseline interaction/spline models; joi250066supp3_prod_1761597796.4701.pdf — p. 25, eFigure 5: center graph; joi250066supp3_prod_1761597796.4701.pdf — p. 27, eFigure 7: post hoc forest</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G6" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$7,A6)&lt;&gt;1,LEFT(A6,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J6" s="22">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),OR(E6="report_internal_inconsistency",E6="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>substantive_difference</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="23" t="n"/>
+      <c r="O6" s="23" t="n"/>
+      <c r="P6" s="23" t="n"/>
+      <c r="Q6" s="23" t="n"/>
+      <c r="R6" s="22" t="inlineStr">
+        <is>
+          <t>SAP p12 7.2 and addendum pp14-15 (4 Oct 2024): 7 prespecified subgroup interactions (age, sex, distal motor function, cortical dysfunction, SSRI, stroke type, baseline FMA &lt;median vs &gt;=median) in a forest plot; SAP p11: center and treatment-by-center terms in the main model; protocol v1.4 p86 11.4.3: stroke-type interaction and covariate-adjusted sensitivity analyses. None is reported (supp3 index p1; eFigure 7 p27 shows only post hoc PH1-PH3). Report labels the FMA &lt;=35/&gt;35 subgroup and the center plot post hoc, although the plan prespecified a median split (median 34) and the center display. Main p5 says prespecified analyses were performed as outlined. Card agrees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1" s="25">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C006</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Serious-event hierarchy counts do not reconcile with their parent totals</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Table 2, levodopa serious-event parent and all 13 top-level category rows; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Table 2, placebo infection parent and all six infection subtype rows; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Adverse Events narrative and table notes: corroborating event totals and unit context</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>retain</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>primary_done</t>
+        </is>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$7,A7)&lt;&gt;1,LEFT(A7,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>probable_issue</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>minor_presentation</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="K7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),OR(E7="report_internal_inconsistency",E7="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L7" s="22">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+      <c r="R7" s="22" t="inlineStr">
+        <is>
+          <t>Main p6 Table 2 (rendered): levodopa top-level SAE categories sum to 143 vs parent 126; placebo 139 vs 129. Infection subtypes sum to 59 vs 55 (levodopa) and 52 vs 44 (placebo). Stroke (15+1, 18+1) and cardiac (5+5+2, 1+2+0) subtypes reconcile; AEs of interest reconcile (79, 67). No note says an event may count in several categories, and 'Other (none of the above)' implies exclusive coding. Counts are integers, so rounding does not apply; all four comparisons fail, not only the two the card registered.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R7"/>
+  <conditionalFormatting sqref="H2:H7">
+    <cfRule type="expression" priority="8" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I7">
+    <cfRule type="expression" priority="9" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J7">
+    <cfRule type="expression" priority="10" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K7">
+    <cfRule type="expression" priority="11" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),OR($E2="report_internal_inconsistency",$E2="plan_material")))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L7">
+    <cfRule type="expression" priority="12" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="protocol_report"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G7">
+    <cfRule type="expression" priority="13" dxfId="71">
+      <formula>G2&lt;&gt;"PRIMARY READY"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation sqref="D2:D7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"retain,exclude,discuss"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"statistical_results,report_internal_inconsistency,plan_material,protocol_report"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"no,primary_done"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"confirmed_issue,probable_issue,not_issue,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive,minor_presentation,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"direct,possible,unlikely,unknown,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_inconsistency,minor_presentation,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_difference,minor_presentation,version_timing,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
